--- a/test/standard_mapping/input.xlsx
+++ b/test/standard_mapping/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Program\VScode\workspace\data-governance\test\standard_mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBCCD93-1225-4629-BAAC-5DA695963F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC2E16F-6CE9-4D51-906F-82C26DC8AC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8621" uniqueCount="2712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8621" uniqueCount="2713">
   <si>
     <t>上游信息</t>
   </si>
@@ -8222,6 +8222,10 @@
   </si>
   <si>
     <t>1. 因为关键信息：字段名'数据权限代码KEY值1'，业务定义'角色数据权限维护功能维护的数据权限代码KEY值1（共5个属性）'。字段含'代码'和'KEY值'，表明该数据项是'数据权限代码'这一结构化代码中的键（KEY）取值，是代码体系的一部分。逐一对照六类：编码类适用于'被赋予具有一定规律、易于计算机和人识别处理的符号'，KEY值作为数据权限代码结构的组成键，具有明确代码语义，符合编码类；文本类适用于自由说明描述，而KEY值是代码结构的组成部分，并非普通描述文本；数值类需数量、金额等语义，KEY值不一定是数字含义，不符合；日期时间类、标志类（仅是否）、代码枚举类（无类型/状态等分类语义，且是代码键值而非枚举分类）均不符合。权衡：应属编码类。申请单填写'文本类'，与实际判断不一致，故is_correct为false，correct_type为编码类。，当前字段所属类型可能错误，应为编码类，请联系业务确认</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码枚举类</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9789,7 +9793,7 @@
         <v>46</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>51</v>
+        <v>2712</v>
       </c>
       <c r="V33" s="1" t="s">
         <v>52</v>
